--- a/AAA.xlsx
+++ b/AAA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17775" tabRatio="600" firstSheet="4" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="4" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="History" sheetId="1" state="visible" r:id="rId1"/>
@@ -433,12 +433,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -563,7 +578,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
@@ -575,34 +590,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
@@ -687,7 +702,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -707,7 +722,18 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1264,184 +1290,184 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>VariableName</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>CustomStorageClass</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>DataType</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>InitialValue</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>HeaderFile</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>DefinitionFile</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Dimensions</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Complexity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>SignalA</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>myPackage</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>YS_SelectRAMSignal</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Bus: FaultBus</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr"/>
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>MCU_Fault_Signals.h</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>MCU_Fault_Signals.c</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>故障状态信号总线</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr"/>
+      <c r="K2" s="12" t="inlineStr"/>
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M2" s="5" t="n">
+      <c r="M2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>real</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>SignalB</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>myPackage</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>ExportedGlobal</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr"/>
+      <c r="G3" s="12" t="inlineStr"/>
+      <c r="H3" s="12" t="inlineStr"/>
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>位置反馈信号</t>
         </is>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K3" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="M3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>real</t>
         </is>
@@ -1493,196 +1519,196 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>VariableName</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>CustomStorageClass</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>DataType</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>InitialValue</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>HeaderFile</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>DefinitionFile</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Dimensions</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Complexity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>ParamA</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>myPackage</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>YS_SelectRAMPara</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F2" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>MCU_Fault_Paras.h</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>MCU_Fault_Paras.c</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>A相电流故障限值设置</t>
         </is>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J2" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="K2" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>[1 1]</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N2" s="11" t="inlineStr">
         <is>
           <t>real</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>ParamB</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>myPackage</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>ExportedGlobal</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="11" t="n">
         <v>0.35</v>
       </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr"/>
+      <c r="H3" s="11" t="inlineStr"/>
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>速度环比例系数</t>
         </is>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K3" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>[1 1]</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="11" t="inlineStr">
         <is>
           <t>real</t>
         </is>
@@ -1691,12 +1717,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ParamBCopy</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>myPackage</t>
+          <t>Simulink</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1706,38 +1732,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ExportedGlobal</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.35</v>
-      </c>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>速度环比例系数</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[1 1]</t>
+          <t>[0 0]</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1749,7 +1761,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ParamACopy</t>
+          <t>Param</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1764,46 +1776,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YS_SelectRAMPara</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>600</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MCU_Fault_Paras.h</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>MCU_Fault_Paras.c</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>A相电流故障限值设置</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[1 1]</t>
+          <t>[0 0]</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1814,22 +1804,22 @@
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B3 B4:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Config!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C3 C4:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Config!$B$3:$B$3</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D3 D4:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Config!$C$2:$C$7</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E3 E4:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Config!$D$2:$D$9</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L3 L4:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Config!$E$2:$E$9</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N3 N4:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Config!$G$2:$G$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -1844,8 +1834,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col width="8.71666666666667" customWidth="1" style="7" min="1" max="1"/>
     <col width="6.375" customWidth="1" style="7" min="2" max="2"/>
@@ -1890,26 +1880,6 @@
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>Define.h</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ModeCopy</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
         <is>
           <t>Define.h</t>
         </is>
@@ -2220,17 +2190,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CtrlBus</t>
+          <t>FaultBus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>IcSensorFault</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -2238,29 +2208,29 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>位置矢量</t>
+          <t>电流传感器故障标志</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CtrlBus</t>
+          <t>FaultBus</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Velocity</t>
+          <t>VoltageFault</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -2268,12 +2238,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>速度矢量</t>
+          <t>母线电压故障标志</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2285,42 +2255,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IcSensorFault</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>uint8</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>电流传感器故障标志</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FaultBus</t>
+          <t>CtrlBus</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VoltageFault</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -2328,24 +2290,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>母线电压故障标志</t>
+          <t>位置矢量</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FaultBus</t>
+          <t>CtrlBus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2356,8 +2318,16 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>速度矢量</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
